--- a/Dokumentation/DWH_Mapping_Fakten_Dimensionen_v3.xlsx
+++ b/Dokumentation/DWH_Mapping_Fakten_Dimensionen_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaeseberg\Github\DVS\Dokumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123846F9-5220-4465-A1B4-5C9BF47BF57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D0C8DD-D6DF-49E4-AE2A-27F4D201C5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1515,8 +1515,8 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="31.265625" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="3" max="3" width="19.73046875" customWidth="1"/>
+    <col min="4" max="4" width="51.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="44" customWidth="1"/>

--- a/Dokumentation/DWH_Mapping_Fakten_Dimensionen_v3.xlsx
+++ b/Dokumentation/DWH_Mapping_Fakten_Dimensionen_v3.xlsx
@@ -8,21 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaeseberg\Github\DVS\Dokumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D0C8DD-D6DF-49E4-AE2A-27F4D201C5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD79EBC-E921-4043-ABDB-51AD35D37A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fakten" sheetId="1" r:id="rId1"/>
     <sheet name="Dimensionen" sheetId="2" r:id="rId2"/>
-    <sheet name="Änderungen" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="200">
   <si>
     <t>Frage-
 stellung</t>
@@ -627,127 +626,13 @@
   </si>
   <si>
     <t>Bitte eine der beiden Varianten festlegen. Bis dahin ist die Spalte Kunde in dieser Datei als offen markiert.</t>
-  </si>
-  <si>
-    <t>Nr.</t>
-  </si>
-  <si>
-    <t>Bereich</t>
-  </si>
-  <si>
-    <t>Änderung / Punkt</t>
-  </si>
-  <si>
-    <t>Begründung</t>
-  </si>
-  <si>
-    <t>Quellsysteme</t>
-  </si>
-  <si>
-    <t>Ticketsystem und Inventarsystem sind jetzt zwei getrennte Datenbanken (01_init_ticketsystem.sql, 01_init_inventarsystem.sql) statt zwei Schemas in einer Datenbank</t>
-  </si>
-  <si>
-    <t>Entspricht dem Szenario aus der Doku (zwei getrennt gepflegte Systeme)</t>
-  </si>
-  <si>
-    <t>Fakten Frage 1</t>
-  </si>
-  <si>
-    <t>Business-Tabelle und -Spalten an das neue Star Schema angepasst: SLA_Bearbeitung_Facts mit Ticket_NR, Bearbeitung_NR, Geraet_SK, Standort_SK, Mitarbeiter_SK, Prioritaet_SK, Datum_SK, Bearbeitungszeit_Minuten, SLA_Zielzeit_Minuten, SLA_Abweichung_Minuten</t>
-  </si>
-  <si>
-    <t>Übernahme des vom Nutzer vorgegebenen Star Schemas</t>
-  </si>
-  <si>
-    <t>Keine eigene Kunden-Dimension mehr, Kunde ist stattdessen Attribut von Dim_Standort</t>
-  </si>
-  <si>
-    <t>Entspricht dem vorgegebenen Star Schema, siehe aber offenen Punkt unten</t>
-  </si>
-  <si>
-    <t>SLA_Eingehalten (vorheriger Vorschlag) nicht mehr enthalten</t>
-  </si>
-  <si>
-    <t>Nicht Teil des vorgegebenen Star Schemas, kann bei Bedarf ergänzt werden</t>
-  </si>
-  <si>
-    <t>Fakten Frage 2</t>
-  </si>
-  <si>
-    <t>Business-Tabelle und -Spalten angepasst: Wartung_Kosten_Facts mit Geraetetyp_SK, Standort_SK, Datum_SK, Wartungskosten, Vertragskosten_pro_Jahr, Anzahl_Tickets</t>
-  </si>
-  <si>
-    <t>Dim_Contract_Type und Vertragsart entfallen vollständig</t>
-  </si>
-  <si>
-    <t>Nicht Teil des vorgegebenen Star Schemas, vereinfacht die Aggregation</t>
-  </si>
-  <si>
-    <t>Dimensionen</t>
-  </si>
-  <si>
-    <t>Dim_Standort und Dim_Datum als gemeinsame Dimensionen für beide Fragestellungen geführt</t>
-  </si>
-  <si>
-    <t>Beide Star Schemas verwenden dieselben Dimensionen (konformierte Dimensionen)</t>
-  </si>
-  <si>
-    <t>Schlüssel- und Spaltennamen an das Star Schema angepasst (z. B. Geraet_SK statt DEVICE_KEY, Prioritaet_NK statt PRIORITY_KEY)</t>
-  </si>
-  <si>
-    <t>Konsistenz mit den vom Nutzer gelieferten Diagrammen</t>
-  </si>
-  <si>
-    <t>Core-Schicht</t>
-  </si>
-  <si>
-    <t>Je Dimension eine eigene Core-Tabelle mit natürlichem Schlüssel ergänzt: Core_Geraet, Core_Mitarbeiter, Core_Prioritaet, Core_Geraetetyp, Core_Standort, Core_Datum</t>
-  </si>
-  <si>
-    <t>Die Aufgabenstellung nennt für Core zwei getrennte Bestandteile, Topic-Tabellen je Fragestellung UND den Aufbau aller benötigten Dimensionen. Vorher steckten die Dimensionsattribute nur in den Topic-Tabellen</t>
-  </si>
-  <si>
-    <t>Business-Dimensionen (Dim_Geraet, Dim_Mitarbeiter, Dim_Prioritaet, Dim_Geraetetyp, Dim_Standort, Dim_Datum) werden jetzt aus den neuen Core-Dimensionstabellen geladen, nicht mehr direkt per Distinct aus den Topic-Tabellen</t>
-  </si>
-  <si>
-    <t>Entspricht dem in der Aufgabenstellung beschriebenen Ablauf: Core bildet die Dimensionen, Business ersetzt die natürlichen Schlüssel durch künstliche Schlüssel</t>
-  </si>
-  <si>
-    <t>Offene Punkte, die vor der Umsetzung geklärt werden sollten</t>
-  </si>
-  <si>
-    <t>Offen</t>
-  </si>
-  <si>
-    <t>Dim_Standort.Kunde ist mit den aktuellen Beispieldaten nicht eindeutig befüllbar (siehe Hinweis im Blatt Dimensionen). Bitte Variante a oder b wählen.</t>
-  </si>
-  <si>
-    <t>StandortID und KundenNr werden im Generator unabhängig vergeben, ein Standort kann mehrere Kunden haben</t>
-  </si>
-  <si>
-    <t>Vertragskosten_pro_Jahr wird bei Monatsgranularität als Kosten_pro_Jahr / 12 je Monat geladen. Spaltenname beibehalten oder in Vertragskosten_Monat umbenennen?</t>
-  </si>
-  <si>
-    <t>Sonst ergibt die Summe über ein Jahr das Zwölffache des tatsächlichen Vertragswerts</t>
-  </si>
-  <si>
-    <t>Datum_SK für Vertragskosten: pro Vertrag muss für jeden Monat der Laufzeit eine eigene Zeile mit dem jeweiligen Monatsersten erzeugt werden (Monatsreihe je Vertrag)</t>
-  </si>
-  <si>
-    <t>Ein Vertrag deckt in der Regel mehrere Monate ab, die Faktentabelle ist aber monatsgranular</t>
-  </si>
-  <si>
-    <t>Sortierreihenfolge für Dim_Prioritaet (Kritisch vor Hoch vor Normal) ist im Star Schema nicht vorgesehen. Ohne sie sortieren Grafiken alphabetisch.</t>
-  </si>
-  <si>
-    <t>Nur relevant, falls die Priorität in Diagrammen sortiert dargestellt werden soll</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,11 +651,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1014,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1157,11 +1037,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1527,28 +1402,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="64" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="53" t="s">
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="60"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="57"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="67"/>
+      <c r="A2" s="64"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1581,7 +1456,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1614,7 +1489,7 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="62"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
@@ -1645,7 +1520,7 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="62"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="16" t="s">
         <v>23</v>
       </c>
@@ -1674,7 +1549,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" s="62"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="16" t="s">
         <v>23</v>
       </c>
@@ -1693,7 +1568,7 @@
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="62"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="16" t="s">
         <v>23</v>
       </c>
@@ -1724,7 +1599,7 @@
       <c r="K7" s="9"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="62"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="16" t="s">
         <v>23</v>
       </c>
@@ -1753,7 +1628,7 @@
       <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="62"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
@@ -1782,7 +1657,7 @@
       <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="62"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="10" t="s">
         <v>36</v>
       </c>
@@ -1801,7 +1676,7 @@
       <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="62"/>
+      <c r="A11" s="59"/>
       <c r="B11" s="10" t="s">
         <v>36</v>
       </c>
@@ -1832,7 +1707,7 @@
       <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A12" s="62"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="10" t="s">
         <v>36</v>
       </c>
@@ -1863,7 +1738,7 @@
       <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="62"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="10" t="s">
         <v>36</v>
       </c>
@@ -1892,7 +1767,7 @@
       <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="63"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="22"/>
       <c r="C14" s="23"/>
       <c r="D14" s="24"/>
@@ -1911,7 +1786,7 @@
       <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="54" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1940,7 +1815,7 @@
       <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="58"/>
+      <c r="A16" s="55"/>
       <c r="B16" s="10" t="s">
         <v>9</v>
       </c>
@@ -1971,7 +1846,7 @@
       <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="58"/>
+      <c r="A17" s="55"/>
       <c r="B17" s="10" t="s">
         <v>9</v>
       </c>
@@ -2002,7 +1877,7 @@
       <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="58"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="16" t="s">
         <v>66</v>
       </c>
@@ -2021,7 +1896,7 @@
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="58"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="16" t="s">
         <v>66</v>
       </c>
@@ -2048,7 +1923,7 @@
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A20" s="58"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="16" t="s">
         <v>66</v>
       </c>
@@ -2075,7 +1950,7 @@
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="58"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="16" t="s">
         <v>66</v>
       </c>
@@ -2104,7 +1979,7 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="58"/>
+      <c r="A22" s="55"/>
       <c r="B22" s="16" t="s">
         <v>66</v>
       </c>
@@ -2137,7 +2012,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" s="58"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="10" t="s">
         <v>83</v>
       </c>
@@ -2156,7 +2031,7 @@
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="58"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="10" t="s">
         <v>83</v>
       </c>
@@ -2187,7 +2062,7 @@
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A25" s="58"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="10" t="s">
         <v>83</v>
       </c>
@@ -2216,7 +2091,7 @@
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A26" s="58"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="16" t="s">
         <v>23</v>
       </c>
@@ -2235,7 +2110,7 @@
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A27" s="58"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="16" t="s">
         <v>23</v>
       </c>
@@ -2264,7 +2139,7 @@
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="59"/>
+      <c r="A28" s="56"/>
       <c r="B28" s="31" t="s">
         <v>23</v>
       </c>
@@ -2415,28 +2290,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="64" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="53" t="s">
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="60"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="57"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="67"/>
+      <c r="A2" s="64"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2469,7 +2344,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="68" t="s">
         <v>113</v>
       </c>
       <c r="B3" s="36" t="s">
@@ -2500,7 +2375,7 @@
       <c r="K3" s="36"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" s="72"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="37" t="s">
         <v>9</v>
       </c>
@@ -2529,7 +2404,7 @@
       <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="72"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="37" t="s">
         <v>9</v>
       </c>
@@ -2558,7 +2433,7 @@
       <c r="K5" s="37"/>
     </row>
     <row r="6" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A6" s="72"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="38" t="s">
@@ -2581,7 +2456,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="72"/>
+      <c r="A7" s="69"/>
       <c r="B7" s="36" t="s">
         <v>126</v>
       </c>
@@ -2610,7 +2485,7 @@
       <c r="K7" s="36"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="72"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="37" t="s">
         <v>126</v>
       </c>
@@ -2639,7 +2514,7 @@
       <c r="K8" s="37"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="72"/>
+      <c r="A9" s="69"/>
       <c r="B9" s="37" t="s">
         <v>126</v>
       </c>
@@ -2668,7 +2543,7 @@
       <c r="K9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A10" s="72"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="38"/>
       <c r="C10" s="38"/>
       <c r="D10" s="38" t="s">
@@ -2691,7 +2566,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="72"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="36" t="s">
         <v>23</v>
       </c>
@@ -2720,7 +2595,7 @@
       <c r="K11" s="36"/>
     </row>
     <row r="12" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A12" s="73"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="D12" s="40" t="s">
@@ -2743,7 +2618,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="71" t="s">
         <v>146</v>
       </c>
       <c r="B14" s="43" t="s">
@@ -2774,7 +2649,7 @@
       <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A15" s="75"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
       <c r="D15" s="40" t="s">
@@ -2797,7 +2672,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="65" t="s">
         <v>154</v>
       </c>
       <c r="B17" s="45" t="s">
@@ -2828,7 +2703,7 @@
       <c r="K17" s="45"/>
     </row>
     <row r="18" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A18" s="69"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="46" t="s">
         <v>155</v>
       </c>
@@ -2857,7 +2732,7 @@
       <c r="K18" s="46"/>
     </row>
     <row r="19" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="69"/>
+      <c r="A19" s="66"/>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
       <c r="D19" s="47" t="s">
@@ -2880,7 +2755,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="69"/>
+      <c r="A20" s="66"/>
       <c r="B20" s="38"/>
       <c r="C20" s="38"/>
       <c r="D20" s="38" t="s">
@@ -2903,7 +2778,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A21" s="69"/>
+      <c r="A21" s="66"/>
       <c r="B21" s="45" t="s">
         <v>173</v>
       </c>
@@ -2932,7 +2807,7 @@
       <c r="K21" s="45"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A22" s="69"/>
+      <c r="A22" s="66"/>
       <c r="B22" s="46" t="s">
         <v>173</v>
       </c>
@@ -2961,7 +2836,7 @@
       <c r="K22" s="46"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" s="69"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="46" t="s">
         <v>173</v>
       </c>
@@ -2990,7 +2865,7 @@
       <c r="K23" s="46"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="69"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="46" t="s">
         <v>173</v>
       </c>
@@ -3019,7 +2894,7 @@
       <c r="K24" s="46"/>
     </row>
     <row r="25" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A25" s="70"/>
+      <c r="A25" s="67"/>
       <c r="B25" s="40"/>
       <c r="C25" s="40"/>
       <c r="D25" s="40" t="s">
@@ -3115,227 +2990,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="51">
-        <v>1</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="51">
-        <v>2</v>
-      </c>
-      <c r="B3" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="51">
-        <v>3</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="51">
-        <v>4</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="51">
-        <v>5</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="51">
-        <v>6</v>
-      </c>
-      <c r="B7" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="51">
-        <v>7</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="51">
-        <v>8</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A10" s="51">
-        <v>9</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A11" s="51">
-        <v>10</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B13" s="52" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>237</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" orientation="landscape"/>
-</worksheet>
 </file>